--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2.23606797749979</v>
+        <v>0.3633610463437159</v>
       </c>
       <c r="D2" t="n">
-        <v>36.06706677844699</v>
+        <v>5.860898351497637</v>
       </c>
       <c r="E2" t="n">
-        <v>18.84891480080598</v>
+        <v>3.062948655130971</v>
       </c>
       <c r="F2" t="n">
-        <v>16.92229566287008</v>
+        <v>2.749873045216388</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.55025306102992</v>
+        <v>2.039416122417362</v>
       </c>
       <c r="D3" t="n">
-        <v>28.36806004997265</v>
+        <v>4.609809758120556</v>
       </c>
       <c r="E3" t="n">
-        <v>18.84891480080598</v>
+        <v>3.062948655130971</v>
       </c>
       <c r="F3" t="n">
-        <v>16.92229566287008</v>
+        <v>2.749873045216388</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.26941131052108</v>
+        <v>4.593779337959676</v>
       </c>
       <c r="D4" t="n">
-        <v>28.85156305210647</v>
+        <v>4.688378995967301</v>
       </c>
       <c r="E4" t="n">
-        <v>18.84891480080598</v>
+        <v>3.062948655130971</v>
       </c>
       <c r="F4" t="n">
-        <v>16.92229566287008</v>
+        <v>2.749873045216388</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>58.75592826597221</v>
+        <v>9.547838343220484</v>
       </c>
       <c r="D5" t="n">
-        <v>11.53588068635753</v>
+        <v>1.874580611533099</v>
       </c>
       <c r="E5" t="n">
-        <v>18.84891480080598</v>
+        <v>3.062948655130971</v>
       </c>
       <c r="F5" t="n">
-        <v>16.92229566287008</v>
+        <v>2.749873045216388</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>68.40778826835881</v>
+        <v>11.11626559360831</v>
       </c>
       <c r="D6" t="n">
-        <v>66.3445335369961</v>
+        <v>10.78098669976187</v>
       </c>
       <c r="E6" t="n">
-        <v>18.84891480080598</v>
+        <v>3.062948655130971</v>
       </c>
       <c r="F6" t="n">
-        <v>16.92229566287008</v>
+        <v>2.749873045216388</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.49214226275853</v>
+        <v>6.417473117698261</v>
       </c>
       <c r="D7" t="n">
-        <v>8.353302295030556</v>
+        <v>1.357411622942465</v>
       </c>
       <c r="E7" t="n">
-        <v>18.84891480080598</v>
+        <v>3.062948655130971</v>
       </c>
       <c r="F7" t="n">
-        <v>16.92229566287008</v>
+        <v>2.749873045216388</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.62427398885607</v>
+        <v>5.951444523189111</v>
       </c>
       <c r="D8" t="n">
-        <v>17.9827273314542</v>
+        <v>2.922193191361308</v>
       </c>
       <c r="E8" t="n">
-        <v>18.84891480080598</v>
+        <v>3.062948655130971</v>
       </c>
       <c r="F8" t="n">
-        <v>16.92229566287008</v>
+        <v>2.749873045216388</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.53227585606884</v>
+        <v>5.123994826611187</v>
       </c>
       <c r="D9" t="n">
-        <v>21.47100362537164</v>
+        <v>3.489038089122892</v>
       </c>
       <c r="E9" t="n">
-        <v>18.84891480080598</v>
+        <v>3.062948655130971</v>
       </c>
       <c r="F9" t="n">
-        <v>16.92229566287008</v>
+        <v>2.749873045216388</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.73946408385954</v>
+        <v>6.457662913627175</v>
       </c>
       <c r="D10" t="n">
-        <v>31.72038790788033</v>
+        <v>5.154563035030554</v>
       </c>
       <c r="E10" t="n">
-        <v>18.84891480080598</v>
+        <v>3.062948655130971</v>
       </c>
       <c r="F10" t="n">
-        <v>16.92229566287008</v>
+        <v>2.749873045216388</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>49.93648236283216</v>
+        <v>8.114678383960227</v>
       </c>
       <c r="D11" t="n">
-        <v>51.74622958208873</v>
+        <v>8.408762307089418</v>
       </c>
       <c r="E11" t="n">
-        <v>18.84891480080598</v>
+        <v>3.062948655130971</v>
       </c>
       <c r="F11" t="n">
-        <v>16.92229566287008</v>
+        <v>2.749873045216388</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
